--- a/5225_Project/Ass_1/CloudEco_Project/locust_test.xlsx
+++ b/5225_Project/Ass_1/CloudEco_Project/locust_test.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17440" windowHeight="13160"/>
+    <workbookView windowWidth="22460" windowHeight="13660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t>1 pod</t>
   </si>
@@ -42,6 +43,42 @@
   </si>
   <si>
     <t>RPS</t>
+  </si>
+  <si>
+    <t>Failure</t>
+  </si>
+  <si>
+    <t>5min/user+1</t>
+  </si>
+  <si>
+    <t>（1 time high response time 6800)</t>
+  </si>
+  <si>
+    <t>(12000,13000,3.1)</t>
+  </si>
+  <si>
+    <t>(16000,18000,3)</t>
+  </si>
+  <si>
+    <t>(20000,76000,6)</t>
+  </si>
+  <si>
+    <t>2 pod</t>
+  </si>
+  <si>
+    <t>2min/user+5</t>
+  </si>
+  <si>
+    <t>4 pod</t>
+  </si>
+  <si>
+    <t>8 pod</t>
+  </si>
+  <si>
+    <t>pods</t>
+  </si>
+  <si>
+    <t>max_users</t>
   </si>
 </sst>
 </file>
@@ -215,12 +252,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -541,7 +584,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -565,16 +608,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -583,90 +626,96 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -947,6 +996,1862 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Pods vs Maximum Acceptable Users</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet2!$B$1:$E$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="0"/>
+        <c:axId val="761566656"/>
+        <c:axId val="465899394"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="761566656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t>pod</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-CN"/>
+                  <a:t>s number</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="465899394"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="465899394"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t>max acceptable users</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="761566656"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Pods vs Throughput (RPS)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet2!$B$6:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$7:$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="0"/>
+        <c:axId val="668531791"/>
+        <c:axId val="625074687"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="668531791"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-CN"/>
+                  <a:t>pods number</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="625074687"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="625074687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-CN"/>
+                  <a:t>t</a:t>
+                </a:r>
+                <a:r>
+                  <a:t>hroughput (RPS)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="668531791"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>169545</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>118745</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="5099685" y="445770"/>
+        <a:ext cx="4826000" cy="2875280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>172085</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>109220</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>121285</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>210820</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="5102225" y="3522980"/>
+        <a:ext cx="4826000" cy="2875280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1197,16 +3102,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:F79"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="11.8557692307692" customWidth="1"/>
     <col min="3" max="3" width="16.0192307692308" customWidth="1"/>
     <col min="4" max="4" width="16.6826923076923" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1221,8 +3126,14 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
       <c r="B2">
         <v>1</v>
       </c>
@@ -1236,7 +3147,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="B3">
         <v>2</v>
       </c>
@@ -1247,16 +3158,1114 @@
         <v>430</v>
       </c>
       <c r="E3">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="B4">
         <v>3</v>
+      </c>
+      <c r="C4">
+        <v>530</v>
+      </c>
+      <c r="D4">
+        <v>620</v>
+      </c>
+      <c r="E4">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>730</v>
+      </c>
+      <c r="D5">
+        <v>820</v>
+      </c>
+      <c r="E5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>930</v>
+      </c>
+      <c r="D6">
+        <v>1000</v>
+      </c>
+      <c r="E6">
+        <v>5.7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+      <c r="D7">
+        <v>1100</v>
+      </c>
+      <c r="E7">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>1200</v>
+      </c>
+      <c r="D8">
+        <v>1300</v>
+      </c>
+      <c r="E8">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>1400</v>
+      </c>
+      <c r="D9">
+        <v>1500</v>
+      </c>
+      <c r="E9">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>1500</v>
+      </c>
+      <c r="D10">
+        <v>1600</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>1700</v>
+      </c>
+      <c r="D11">
+        <v>1800</v>
+      </c>
+      <c r="E11">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>1800</v>
+      </c>
+      <c r="D12">
+        <v>1900</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>2000</v>
+      </c>
+      <c r="D13">
+        <v>2100</v>
+      </c>
+      <c r="E13">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>2200</v>
+      </c>
+      <c r="D14">
+        <v>2300</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>2400</v>
+      </c>
+      <c r="D15">
+        <v>2500</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>2500</v>
+      </c>
+      <c r="D16">
+        <v>2600</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>2600</v>
+      </c>
+      <c r="D17">
+        <v>2700</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="2:6">
+      <c r="B18" s="1">
+        <v>17</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2900</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="1">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>3400</v>
+      </c>
+      <c r="D19">
+        <v>3500</v>
+      </c>
+      <c r="E19">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>4300</v>
+      </c>
+      <c r="D20">
+        <v>4500</v>
+      </c>
+      <c r="E20">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21">
+        <v>30</v>
+      </c>
+      <c r="C21">
+        <v>5000</v>
+      </c>
+      <c r="D21">
+        <v>5100</v>
+      </c>
+      <c r="E21">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22">
+        <v>35</v>
+      </c>
+      <c r="C22">
+        <v>6000</v>
+      </c>
+      <c r="D22">
+        <v>6200</v>
+      </c>
+      <c r="E22">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23">
+        <v>40</v>
+      </c>
+      <c r="C23">
+        <v>6600</v>
+      </c>
+      <c r="D23">
+        <v>6800</v>
+      </c>
+      <c r="E23">
+        <v>5.8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24">
+        <v>45</v>
+      </c>
+      <c r="C24">
+        <v>7600</v>
+      </c>
+      <c r="D24">
+        <v>7800</v>
+      </c>
+      <c r="E24">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25">
+        <v>50</v>
+      </c>
+      <c r="C25">
+        <v>8400</v>
+      </c>
+      <c r="D25">
+        <v>8700</v>
+      </c>
+      <c r="E25">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26">
+        <v>55</v>
+      </c>
+      <c r="C26">
+        <v>9100</v>
+      </c>
+      <c r="D26">
+        <v>9300</v>
+      </c>
+      <c r="E26">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27">
+        <v>60</v>
+      </c>
+      <c r="C27">
+        <v>10000</v>
+      </c>
+      <c r="D27">
+        <v>11000</v>
+      </c>
+      <c r="E27">
+        <v>5.9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28">
+        <v>65</v>
+      </c>
+      <c r="C28">
+        <v>11000</v>
+      </c>
+      <c r="D28">
+        <v>12000</v>
+      </c>
+      <c r="E28">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29">
+        <v>70</v>
+      </c>
+      <c r="C29">
+        <v>12000</v>
+      </c>
+      <c r="D29">
+        <v>13000</v>
+      </c>
+      <c r="E29">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30">
+        <v>80</v>
+      </c>
+      <c r="C30">
+        <v>13000</v>
+      </c>
+      <c r="D30">
+        <v>14000</v>
+      </c>
+      <c r="E30">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31">
+        <v>90</v>
+      </c>
+      <c r="C31">
+        <v>15000</v>
+      </c>
+      <c r="D31">
+        <v>16000</v>
+      </c>
+      <c r="E31">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32">
+        <v>100</v>
+      </c>
+      <c r="C32">
+        <v>17000</v>
+      </c>
+      <c r="D32">
+        <v>17000</v>
+      </c>
+      <c r="E32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="B33">
+        <v>120</v>
+      </c>
+      <c r="C33">
+        <v>20000</v>
+      </c>
+      <c r="D33">
+        <v>21000</v>
+      </c>
+      <c r="E33">
+        <v>5.9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="B34">
+        <v>140</v>
+      </c>
+      <c r="C34">
+        <v>23000</v>
+      </c>
+      <c r="D34">
+        <v>24000</v>
+      </c>
+      <c r="E34">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="B35">
+        <v>180</v>
+      </c>
+      <c r="C35">
+        <v>30000</v>
+      </c>
+      <c r="D35">
+        <v>31000</v>
+      </c>
+      <c r="E35">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="B36">
+        <v>200</v>
+      </c>
+      <c r="C36">
+        <v>34000</v>
+      </c>
+      <c r="D36">
+        <v>35000</v>
+      </c>
+      <c r="E36">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="B37">
+        <v>240</v>
+      </c>
+      <c r="C37">
+        <v>41000</v>
+      </c>
+      <c r="D37">
+        <v>42000</v>
+      </c>
+      <c r="E37">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="B38">
+        <v>300</v>
+      </c>
+      <c r="C38">
+        <v>51000</v>
+      </c>
+      <c r="D38">
+        <v>52000</v>
+      </c>
+      <c r="E38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39">
+        <v>350</v>
+      </c>
+      <c r="C39">
+        <v>59000</v>
+      </c>
+      <c r="D39">
+        <v>60000</v>
+      </c>
+      <c r="E39">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40">
+        <v>400</v>
+      </c>
+      <c r="C40">
+        <v>68000</v>
+      </c>
+      <c r="D40">
+        <v>69000</v>
+      </c>
+      <c r="E40">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41">
+        <v>450</v>
+      </c>
+      <c r="C41">
+        <v>76000</v>
+      </c>
+      <c r="D41">
+        <v>77000</v>
+      </c>
+      <c r="E41">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42">
+        <v>600</v>
+      </c>
+      <c r="C42">
+        <v>102000</v>
+      </c>
+      <c r="D42">
+        <v>103000</v>
+      </c>
+      <c r="E42">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="B43">
+        <v>1000</v>
+      </c>
+      <c r="C43">
+        <v>137000</v>
+      </c>
+      <c r="D43">
+        <v>138000</v>
+      </c>
+      <c r="E43">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47">
+        <v>5</v>
+      </c>
+      <c r="C47">
+        <v>340</v>
+      </c>
+      <c r="D47">
+        <v>550</v>
+      </c>
+      <c r="E47">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48">
+        <v>10</v>
+      </c>
+      <c r="C48">
+        <v>780</v>
+      </c>
+      <c r="D48">
+        <v>870</v>
+      </c>
+      <c r="E48">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="B49">
+        <v>15</v>
+      </c>
+      <c r="C49">
+        <v>1000</v>
+      </c>
+      <c r="D49">
+        <v>1400</v>
+      </c>
+      <c r="E49">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="B50">
+        <v>20</v>
+      </c>
+      <c r="C50">
+        <v>1500</v>
+      </c>
+      <c r="D50">
+        <v>1700</v>
+      </c>
+      <c r="E50">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="B51">
+        <v>25</v>
+      </c>
+      <c r="C51">
+        <v>1800</v>
+      </c>
+      <c r="D51">
+        <v>2300</v>
+      </c>
+      <c r="E51">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="B52">
+        <v>30</v>
+      </c>
+      <c r="C52">
+        <v>2200</v>
+      </c>
+      <c r="D52">
+        <v>2600</v>
+      </c>
+      <c r="E52">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" spans="1:6">
+      <c r="B53" s="2">
+        <v>35</v>
+      </c>
+      <c r="C53" s="2">
+        <v>2500</v>
+      </c>
+      <c r="D53" s="2">
+        <v>3100</v>
+      </c>
+      <c r="E53" s="2">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>4</v>
+      </c>
+      <c r="F56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57">
+        <v>30</v>
+      </c>
+      <c r="C57">
+        <v>1300</v>
+      </c>
+      <c r="D57">
+        <v>1400</v>
+      </c>
+      <c r="E57">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="B58">
+        <v>35</v>
+      </c>
+      <c r="C58">
+        <v>1600</v>
+      </c>
+      <c r="D58">
+        <v>1800</v>
+      </c>
+      <c r="E58">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="B59">
+        <v>40</v>
+      </c>
+      <c r="C59">
+        <v>1800</v>
+      </c>
+      <c r="D59">
+        <v>1900</v>
+      </c>
+      <c r="E59">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="B60">
+        <v>45</v>
+      </c>
+      <c r="C60">
+        <v>2000</v>
+      </c>
+      <c r="D60">
+        <v>2100</v>
+      </c>
+      <c r="E60">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="B61">
+        <v>50</v>
+      </c>
+      <c r="C61">
+        <v>2200</v>
+      </c>
+      <c r="D61">
+        <v>2400</v>
+      </c>
+      <c r="E61">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="B62">
+        <v>55</v>
+      </c>
+      <c r="C62">
+        <v>2400</v>
+      </c>
+      <c r="D62">
+        <v>2600</v>
+      </c>
+      <c r="E62">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="B63">
+        <v>60</v>
+      </c>
+      <c r="C63">
+        <v>2600</v>
+      </c>
+      <c r="D63">
+        <v>2800</v>
+      </c>
+      <c r="E63">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="1:6">
+      <c r="B64" s="1">
+        <v>65</v>
+      </c>
+      <c r="C64" s="1">
+        <v>2900</v>
+      </c>
+      <c r="D64" s="1">
+        <v>3100</v>
+      </c>
+      <c r="E64" s="1">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" t="s">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68">
+        <v>40</v>
+      </c>
+      <c r="C68">
+        <v>1200</v>
+      </c>
+      <c r="D68">
+        <v>1400</v>
+      </c>
+      <c r="E68">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69">
+        <v>45</v>
+      </c>
+      <c r="C69">
+        <v>1400</v>
+      </c>
+      <c r="D69">
+        <v>1600</v>
+      </c>
+      <c r="E69">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70">
+        <v>50</v>
+      </c>
+      <c r="C70">
+        <v>1500</v>
+      </c>
+      <c r="D70">
+        <v>1700</v>
+      </c>
+      <c r="E70">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71">
+        <v>55</v>
+      </c>
+      <c r="C71">
+        <v>1700</v>
+      </c>
+      <c r="D71">
+        <v>1900</v>
+      </c>
+      <c r="E71">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72">
+        <v>60</v>
+      </c>
+      <c r="C72">
+        <v>1800</v>
+      </c>
+      <c r="D72">
+        <v>2000</v>
+      </c>
+      <c r="E72">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73">
+        <v>65</v>
+      </c>
+      <c r="C73">
+        <v>2000</v>
+      </c>
+      <c r="D73">
+        <v>2100</v>
+      </c>
+      <c r="E73">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74">
+        <v>70</v>
+      </c>
+      <c r="C74">
+        <v>2100</v>
+      </c>
+      <c r="D74">
+        <v>2300</v>
+      </c>
+      <c r="E74">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75">
+        <v>75</v>
+      </c>
+      <c r="C75">
+        <v>2300</v>
+      </c>
+      <c r="D75">
+        <v>2500</v>
+      </c>
+      <c r="E75">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76">
+        <v>80</v>
+      </c>
+      <c r="C76">
+        <v>2400</v>
+      </c>
+      <c r="D76">
+        <v>2600</v>
+      </c>
+      <c r="E76">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77">
+        <v>85</v>
+      </c>
+      <c r="C77">
+        <v>2600</v>
+      </c>
+      <c r="D77">
+        <v>2800</v>
+      </c>
+      <c r="E77">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="B78">
+        <v>90</v>
+      </c>
+      <c r="C78">
+        <v>2700</v>
+      </c>
+      <c r="D78">
+        <v>2900</v>
+      </c>
+      <c r="E78">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="1:6">
+      <c r="B79" s="1">
+        <v>95</v>
+      </c>
+      <c r="C79" s="1">
+        <v>2900</v>
+      </c>
+      <c r="D79" s="1">
+        <v>3100</v>
+      </c>
+      <c r="E79" s="1">
+        <v>32.8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="10.0384615384615" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>4</v>
+      </c>
+      <c r="E1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>35</v>
+      </c>
+      <c r="D2">
+        <v>65</v>
+      </c>
+      <c r="E2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>5.8</v>
+      </c>
+      <c r="C7">
+        <v>12.8</v>
+      </c>
+      <c r="D7">
+        <v>22.7</v>
+      </c>
+      <c r="E7">
+        <v>32.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/5225_Project/Ass_1/CloudEco_Project/locust_test.xlsx
+++ b/5225_Project/Ass_1/CloudEco_Project/locust_test.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22460" windowHeight="13660" activeTab="1"/>
+    <workbookView windowWidth="27660" windowHeight="13660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
   <si>
     <t>1 pod</t>
   </si>
@@ -36,37 +37,16 @@
     <t>users</t>
   </si>
   <si>
-    <t>response(50) time</t>
+    <t>response(50)</t>
   </si>
   <si>
-    <t>response(95) time</t>
+    <t>response(95)</t>
   </si>
   <si>
     <t>RPS</t>
   </si>
   <si>
-    <t>Failure</t>
-  </si>
-  <si>
-    <t>5min/user+1</t>
-  </si>
-  <si>
-    <t>（1 time high response time 6800)</t>
-  </si>
-  <si>
-    <t>(12000,13000,3.1)</t>
-  </si>
-  <si>
-    <t>(16000,18000,3)</t>
-  </si>
-  <si>
-    <t>(20000,76000,6)</t>
-  </si>
-  <si>
     <t>2 pod</t>
-  </si>
-  <si>
-    <t>2min/user+5</t>
   </si>
   <si>
     <t>4 pod</t>
@@ -452,12 +432,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -584,7 +579,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -596,34 +591,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -708,17 +703,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1030,7 +1046,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>Pods vs Maximum Acceptable Users</a:t>
+              <a:t>Pods vs maximum acceptable users</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1048,27 +1064,81 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:scatterChart>
+        <c:scatterStyle val="line"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
-          <c:cat>
+          <c:xVal>
             <c:numRef>
               <c:f>Sheet2!$B$1:$E$1</c:f>
               <c:numCache>
@@ -1088,8 +1158,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Sheet2!$B$2:$E$2</c:f>
               <c:numCache>
@@ -1102,30 +1172,29 @@
                   <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>95</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
+          <c:smooth val="0"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="761566656"/>
-        <c:axId val="465899394"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="761566656"/>
+        <c:axId val="905225032"/>
+        <c:axId val="261740715"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="905225032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1151,11 +1220,8 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>pod</a:t>
-                </a:r>
-                <a:r>
                   <a:rPr lang="en-US" altLang="zh-CN"/>
-                  <a:t>s number</a:t>
+                  <a:t>pods number</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US" altLang="zh-CN"/>
               </a:p>
@@ -1171,6 +1237,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1179,8 +1246,8 @@
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1206,15 +1273,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465899394"/>
+        <c:crossAx val="261740715"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="0"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
-        <c:axId val="465899394"/>
+        <c:axId val="261740715"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1253,8 +1317,10 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>max acceptable users</a:t>
+                  <a:rPr lang="en-US" altLang="zh-CN"/>
+                  <a:t>max users</a:t>
                 </a:r>
+                <a:endParaRPr lang="en-US" altLang="zh-CN"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1269,13 +1335,19 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1298,9 +1370,9 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="761566656"/>
+        <c:crossAx val="905225032"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1313,6 +1385,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{ceb2dcc4-0a5b-4727-865d-7c6a2a3508cc}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1380,7 +1457,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>Pods vs Throughput (RPS)</a:t>
+              <a:t>Pods vs throughput (RPS)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1398,27 +1475,81 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:scatterChart>
+        <c:scatterStyle val="line"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
-          <c:cat>
+          <c:xVal>
             <c:numRef>
               <c:f>Sheet2!$B$6:$E$6</c:f>
               <c:numCache>
@@ -1438,8 +1569,8 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:cat>
-          <c:val>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Sheet2!$B$7:$E$7</c:f>
               <c:numCache>
@@ -1452,30 +1583,29 @@
                   <c:v>12.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>22.7</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>32.8</c:v>
+                  <c:v>41.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
+          <c:smooth val="0"/>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="668531791"/>
-        <c:axId val="625074687"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="668531791"/>
+        <c:axId val="546829953"/>
+        <c:axId val="564734964"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="546829953"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1518,6 +1648,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1526,8 +1657,8 @@
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1553,15 +1684,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625074687"/>
+        <c:crossAx val="564734964"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
-        <c:axId val="625074687"/>
+        <c:axId val="564734964"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1601,11 +1729,9 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US" altLang="zh-CN"/>
-                  <a:t>t</a:t>
+                  <a:t>avg RPS</a:t>
                 </a:r>
-                <a:r>
-                  <a:t>hroughput (RPS)</a:t>
-                </a:r>
+                <a:endParaRPr lang="en-US" altLang="zh-CN"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1620,13 +1746,19 @@
           </c:spPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1649,9 +1781,9 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="668531791"/>
+        <c:crossAx val="546829953"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1664,6 +1796,1931 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{304a60fb-7a54-4c57-b744-a6afcab3b1e7}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Users vs p95 latency</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="line"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1 pod</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$A$2:$A$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$B$2:$B$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2300</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2600</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2 pod</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$A$2:$A$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$C$2:$C$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="2">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2300</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2600</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4 pod</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$A$2:$A$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$D$2:$D$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="5">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8 pod</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$A$2:$A$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$E$2:$E$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="5">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2600</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="34825662"/>
+        <c:axId val="35957865"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="34825662"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-CN"/>
+                  <a:t>Concurrent users</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="35957865"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="35957865"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t>p95 latency</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="34825662"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{87b85a8e-8763-45b2-82f6-87cd365bb345}"/>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-CN"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="zh-CN" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Users vs RPS</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="line"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1 pod</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$G$2:$G$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$H$2:$H$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2 pod</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$G$2:$G$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$I$2:$I$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="2">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4 pod</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$G$2:$G$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$J$2:$J$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="5">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>26.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>26.3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>26.7</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>26</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>8 pod</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet3!$G$2:$G$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet3!$K$2:$K$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="5">
+                  <c:v>33.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>41.7</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>42.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>41.3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>41.6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>41.7</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>41.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="828923483"/>
+        <c:axId val="370968853"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="828923483"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-CN"/>
+                  <a:t>Concurrent users</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="370968853"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="370968853"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-CN"/>
+                  <a:t>RPS</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="828923483"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="4"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="6"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{050daffb-80b6-43e4-8666-cd8224a061af}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1777,8 +3834,88 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1805,8 +3942,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1878,14 +4015,25 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1901,21 +4049,18 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
-      <a:effectLst/>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
@@ -1942,10 +4087,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1985,22 +4130,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2104,8 +4250,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2237,19 +4383,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2263,6 +4410,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2283,7 +4441,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2310,8 +4468,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2383,14 +4541,25 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
     <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2406,21 +4575,18 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
-      <a:effectLst/>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
@@ -2447,10 +4613,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -2490,22 +4656,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2609,8 +4776,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2742,23 +4909,251 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10210">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -2768,6 +5163,870 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10210">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2791,25 +6050,25 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>169545</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>457835</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>80010</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>118745</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>407035</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>191770</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvPr id="4" name="图表 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5099685" y="445770"/>
-        <a:ext cx="4826000" cy="2875280"/>
+        <a:off x="4850765" y="80010"/>
+        <a:ext cx="4826000" cy="2885440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2821,16 +6080,81 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>172085</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>109220</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>398780</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>121285</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>347980</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>210820</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="图表 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4791710" y="3327400"/>
+        <a:ext cx="4826000" cy="2885440"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>54610</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>166370</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="8242300" y="697230"/>
+        <a:ext cx="4826000" cy="2885440"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>285115</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>170815</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>234315</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>69215</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2838,8 +6162,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5102225" y="3522980"/>
-        <a:ext cx="4826000" cy="2875280"/>
+        <a:off x="7600315" y="4227195"/>
+        <a:ext cx="4826000" cy="2885440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3102,16 +6426,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F79"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:AF19"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="11.8557692307692" customWidth="1"/>
-    <col min="3" max="3" width="16.0192307692308" customWidth="1"/>
-    <col min="4" max="4" width="16.6826923076923" customWidth="1"/>
+    <col min="2" max="2" width="6.16346153846154" customWidth="1"/>
+    <col min="3" max="4" width="11.6153846153846" customWidth="1"/>
+    <col min="5" max="5" width="9.15384615384615" customWidth="1"/>
+    <col min="9" max="9" width="5.27884615384615" customWidth="1"/>
+    <col min="10" max="10" width="11.7884615384615" customWidth="1"/>
+    <col min="11" max="11" width="11.2596153846154" customWidth="1"/>
+    <col min="16" max="16" width="7.91346153846154" customWidth="1"/>
+    <col min="17" max="17" width="11.7980769230769" customWidth="1"/>
+    <col min="18" max="18" width="11.2692307692308" customWidth="1"/>
+    <col min="23" max="23" width="7.03846153846154" customWidth="1"/>
+    <col min="24" max="24" width="11.4423076923077" customWidth="1"/>
+    <col min="25" max="25" width="11.0865384615385" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:32">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -3126,14 +6460,53 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" t="s">
+        <v>4</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
+    <row r="2" spans="1:32">
       <c r="B2">
         <v>1</v>
       </c>
@@ -3146,1040 +6519,580 @@
       <c r="E2">
         <v>4.5</v>
       </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>340</v>
+      </c>
+      <c r="K2">
+        <v>550</v>
+      </c>
+      <c r="L2">
+        <v>12.7</v>
+      </c>
+      <c r="P2">
+        <v>10</v>
+      </c>
+      <c r="Q2">
+        <v>360</v>
+      </c>
+      <c r="R2">
+        <v>540</v>
+      </c>
+      <c r="S2">
+        <v>26</v>
+      </c>
+      <c r="W2">
+        <v>10</v>
+      </c>
+      <c r="X2">
+        <v>280</v>
+      </c>
+      <c r="Y2">
+        <v>370</v>
+      </c>
+      <c r="Z2">
+        <v>33.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:32">
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>370</v>
+        <v>530</v>
       </c>
       <c r="D3">
-        <v>430</v>
+        <v>620</v>
       </c>
       <c r="E3">
         <v>5.5</v>
       </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3">
+        <v>780</v>
+      </c>
+      <c r="K3">
+        <v>870</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="P3">
+        <v>20</v>
+      </c>
+      <c r="Q3">
+        <v>750</v>
+      </c>
+      <c r="R3">
+        <v>840</v>
+      </c>
+      <c r="S3">
+        <v>26</v>
+      </c>
+      <c r="W3">
+        <v>25</v>
+      </c>
+      <c r="X3">
+        <v>600</v>
+      </c>
+      <c r="Y3">
+        <v>750</v>
+      </c>
+      <c r="Z3">
+        <v>41</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:32">
       <c r="B4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>530</v>
+        <v>930</v>
       </c>
       <c r="D4">
-        <v>620</v>
+        <v>1000</v>
       </c>
       <c r="E4">
-        <v>5.5</v>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="I4">
+        <v>15</v>
+      </c>
+      <c r="J4">
+        <v>1000</v>
+      </c>
+      <c r="K4">
+        <v>1400</v>
+      </c>
+      <c r="L4">
+        <v>13</v>
+      </c>
+      <c r="P4" s="7">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>1100</v>
+      </c>
+      <c r="R4" s="7">
+        <v>1300</v>
+      </c>
+      <c r="S4" s="7">
+        <v>26.2</v>
+      </c>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7">
+        <v>40</v>
+      </c>
+      <c r="X4" s="7">
+        <v>1000</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>1200</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>41.7</v>
+      </c>
+      <c r="AA4" s="7"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:32">
       <c r="B5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>730</v>
+        <v>1200</v>
       </c>
       <c r="D5">
-        <v>820</v>
+        <v>1300</v>
       </c>
       <c r="E5">
-        <v>5.5</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>1500</v>
+      </c>
+      <c r="K5">
+        <v>1700</v>
+      </c>
+      <c r="L5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="7">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>750</v>
+      </c>
+      <c r="R5" s="7">
+        <v>840</v>
+      </c>
+      <c r="S5" s="7">
+        <v>26</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7">
+        <v>55</v>
+      </c>
+      <c r="X5" s="7">
+        <v>1300</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>1500</v>
+      </c>
+      <c r="Z5" s="7">
+        <v>42.4</v>
+      </c>
+      <c r="AA5" s="7"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:32">
       <c r="B6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>930</v>
+        <v>1500</v>
       </c>
       <c r="D6">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="E6">
-        <v>5.7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <v>1800</v>
+      </c>
+      <c r="K6">
+        <v>2300</v>
+      </c>
+      <c r="L6">
+        <v>12.6</v>
+      </c>
+      <c r="P6" s="7">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>1500</v>
+      </c>
+      <c r="R6" s="7">
+        <v>1700</v>
+      </c>
+      <c r="S6" s="7">
+        <v>26.3</v>
+      </c>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
+        <v>70</v>
+      </c>
+      <c r="X6" s="7">
+        <v>1700</v>
+      </c>
+      <c r="Y6" s="7">
+        <v>2000</v>
+      </c>
+      <c r="Z6" s="7">
+        <v>41.3</v>
+      </c>
+      <c r="AA6" s="7"/>
     </row>
-    <row r="7" spans="1:6">
-      <c r="B7">
+    <row r="7" spans="1:32">
+      <c r="B7" s="7">
+        <v>10</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1700</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1800</v>
+      </c>
+      <c r="E7" s="7">
+        <v>5.9</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7">
+        <v>30</v>
+      </c>
+      <c r="J7" s="7">
+        <v>2200</v>
+      </c>
+      <c r="K7" s="7">
+        <v>2600</v>
+      </c>
+      <c r="L7" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7">
+        <v>50</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>1800</v>
+      </c>
+      <c r="R7" s="7">
+        <v>2000</v>
+      </c>
+      <c r="S7" s="7">
+        <v>26</v>
+      </c>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7">
+        <v>85</v>
+      </c>
+      <c r="X7" s="7">
+        <v>2000</v>
+      </c>
+      <c r="Y7" s="7">
+        <v>2200</v>
+      </c>
+      <c r="Z7" s="7">
+        <v>41.6</v>
+      </c>
+      <c r="AA7" s="7"/>
+    </row>
+    <row r="8" spans="1:32">
+      <c r="B8" s="7">
+        <v>11</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1800</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1900</v>
+      </c>
+      <c r="E8" s="7">
         <v>6</v>
       </c>
-      <c r="C7">
-        <v>1000</v>
-      </c>
-      <c r="D7">
-        <v>1100</v>
-      </c>
-      <c r="E7">
-        <v>5.7</v>
-      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9">
+        <v>35</v>
+      </c>
+      <c r="J8" s="9">
+        <v>2500</v>
+      </c>
+      <c r="K8" s="9">
+        <v>3000</v>
+      </c>
+      <c r="L8" s="9">
+        <v>12.8</v>
+      </c>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>2300</v>
+      </c>
+      <c r="R8" s="7">
+        <v>2500</v>
+      </c>
+      <c r="S8" s="7">
+        <v>26.7</v>
+      </c>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7">
+        <v>100</v>
+      </c>
+      <c r="X8" s="7">
+        <v>2400</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>2600</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>41.7</v>
+      </c>
+      <c r="AA8" s="7"/>
     </row>
-    <row r="8" spans="1:6">
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>1200</v>
-      </c>
-      <c r="D8">
-        <v>1300</v>
-      </c>
-      <c r="E8">
+    <row r="9" spans="1:32">
+      <c r="B9" s="7">
+        <v>13</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2200</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2300</v>
+      </c>
+      <c r="E9" s="7">
+        <v>6</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7">
+        <v>70</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>2700</v>
+      </c>
+      <c r="R9" s="7">
+        <v>3000</v>
+      </c>
+      <c r="S9" s="7">
+        <v>26</v>
+      </c>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7">
+        <v>115</v>
+      </c>
+      <c r="X9" s="7">
+        <v>2700</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>3000</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>41.6</v>
+      </c>
+      <c r="AA9" s="7"/>
+    </row>
+    <row r="10" spans="1:32">
+      <c r="B10" s="7">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>2500</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2600</v>
+      </c>
+      <c r="E10" s="7">
+        <v>6</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
+    </row>
+    <row r="11" spans="1:32">
+      <c r="B11" s="7">
+        <v>17</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2900</v>
+      </c>
+      <c r="D11" s="7">
+        <v>3000</v>
+      </c>
+      <c r="E11" s="7">
         <v>5.8</v>
       </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
     </row>
-    <row r="9" spans="1:6">
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9">
-        <v>1400</v>
-      </c>
-      <c r="D9">
-        <v>1500</v>
-      </c>
-      <c r="E9">
-        <v>5.8</v>
-      </c>
+    <row r="12" spans="1:32">
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
     </row>
-    <row r="10" spans="1:6">
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <v>1500</v>
-      </c>
-      <c r="D10">
-        <v>1600</v>
-      </c>
-      <c r="E10">
-        <v>6</v>
-      </c>
+    <row r="13" spans="1:32">
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
     </row>
-    <row r="11" spans="1:6">
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11">
-        <v>1700</v>
-      </c>
-      <c r="D11">
-        <v>1800</v>
-      </c>
-      <c r="E11">
-        <v>5.9</v>
-      </c>
+    <row r="14" spans="1:32">
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
+      <c r="AF14" s="10"/>
     </row>
-    <row r="12" spans="1:6">
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12">
-        <v>1800</v>
-      </c>
-      <c r="D12">
-        <v>1900</v>
-      </c>
-      <c r="E12">
-        <v>6</v>
-      </c>
+    <row r="15" spans="1:32">
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
     </row>
-    <row r="13" spans="1:6">
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13">
-        <v>2000</v>
-      </c>
-      <c r="D13">
-        <v>2100</v>
-      </c>
-      <c r="E13">
-        <v>6.1</v>
-      </c>
+    <row r="16" spans="1:32">
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
     </row>
-    <row r="14" spans="1:6">
-      <c r="B14">
-        <v>13</v>
-      </c>
-      <c r="C14">
-        <v>2200</v>
-      </c>
-      <c r="D14">
-        <v>2300</v>
-      </c>
-      <c r="E14">
-        <v>6</v>
-      </c>
+    <row r="17" spans="15:20">
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
     </row>
-    <row r="15" spans="1:6">
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="C15">
-        <v>2400</v>
-      </c>
-      <c r="D15">
-        <v>2500</v>
-      </c>
-      <c r="E15">
-        <v>6</v>
-      </c>
+    <row r="18" spans="15:20">
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
     </row>
-    <row r="16" spans="1:6">
-      <c r="B16">
-        <v>15</v>
-      </c>
-      <c r="C16">
-        <v>2500</v>
-      </c>
-      <c r="D16">
-        <v>2600</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17">
-        <v>16</v>
-      </c>
-      <c r="C17">
-        <v>2600</v>
-      </c>
-      <c r="D17">
-        <v>2700</v>
-      </c>
-      <c r="E17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="2:6">
-      <c r="B18" s="1">
-        <v>17</v>
-      </c>
-      <c r="C18" s="1">
-        <v>2900</v>
-      </c>
-      <c r="D18" s="1">
-        <v>3000</v>
-      </c>
-      <c r="E18" s="1">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19">
-        <v>20</v>
-      </c>
-      <c r="C19">
-        <v>3400</v>
-      </c>
-      <c r="D19">
-        <v>3500</v>
-      </c>
-      <c r="E19">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>4300</v>
-      </c>
-      <c r="D20">
-        <v>4500</v>
-      </c>
-      <c r="E20">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21">
-        <v>30</v>
-      </c>
-      <c r="C21">
-        <v>5000</v>
-      </c>
-      <c r="D21">
-        <v>5100</v>
-      </c>
-      <c r="E21">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="B22">
-        <v>35</v>
-      </c>
-      <c r="C22">
-        <v>6000</v>
-      </c>
-      <c r="D22">
-        <v>6200</v>
-      </c>
-      <c r="E22">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="B23">
-        <v>40</v>
-      </c>
-      <c r="C23">
-        <v>6600</v>
-      </c>
-      <c r="D23">
-        <v>6800</v>
-      </c>
-      <c r="E23">
-        <v>5.8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24">
-        <v>45</v>
-      </c>
-      <c r="C24">
-        <v>7600</v>
-      </c>
-      <c r="D24">
-        <v>7800</v>
-      </c>
-      <c r="E24">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="B25">
-        <v>50</v>
-      </c>
-      <c r="C25">
-        <v>8400</v>
-      </c>
-      <c r="D25">
-        <v>8700</v>
-      </c>
-      <c r="E25">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="B26">
-        <v>55</v>
-      </c>
-      <c r="C26">
-        <v>9100</v>
-      </c>
-      <c r="D26">
-        <v>9300</v>
-      </c>
-      <c r="E26">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27">
-        <v>60</v>
-      </c>
-      <c r="C27">
-        <v>10000</v>
-      </c>
-      <c r="D27">
-        <v>11000</v>
-      </c>
-      <c r="E27">
-        <v>5.9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6">
-      <c r="B28">
-        <v>65</v>
-      </c>
-      <c r="C28">
-        <v>11000</v>
-      </c>
-      <c r="D28">
-        <v>12000</v>
-      </c>
-      <c r="E28">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="B29">
-        <v>70</v>
-      </c>
-      <c r="C29">
-        <v>12000</v>
-      </c>
-      <c r="D29">
-        <v>13000</v>
-      </c>
-      <c r="E29">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30">
-        <v>80</v>
-      </c>
-      <c r="C30">
-        <v>13000</v>
-      </c>
-      <c r="D30">
-        <v>14000</v>
-      </c>
-      <c r="E30">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="B31">
-        <v>90</v>
-      </c>
-      <c r="C31">
-        <v>15000</v>
-      </c>
-      <c r="D31">
-        <v>16000</v>
-      </c>
-      <c r="E31">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32">
-        <v>100</v>
-      </c>
-      <c r="C32">
-        <v>17000</v>
-      </c>
-      <c r="D32">
-        <v>17000</v>
-      </c>
-      <c r="E32">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="B33">
-        <v>120</v>
-      </c>
-      <c r="C33">
-        <v>20000</v>
-      </c>
-      <c r="D33">
-        <v>21000</v>
-      </c>
-      <c r="E33">
-        <v>5.9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="B34">
-        <v>140</v>
-      </c>
-      <c r="C34">
-        <v>23000</v>
-      </c>
-      <c r="D34">
-        <v>24000</v>
-      </c>
-      <c r="E34">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="B35">
-        <v>180</v>
-      </c>
-      <c r="C35">
-        <v>30000</v>
-      </c>
-      <c r="D35">
-        <v>31000</v>
-      </c>
-      <c r="E35">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="B36">
-        <v>200</v>
-      </c>
-      <c r="C36">
-        <v>34000</v>
-      </c>
-      <c r="D36">
-        <v>35000</v>
-      </c>
-      <c r="E36">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="B37">
-        <v>240</v>
-      </c>
-      <c r="C37">
-        <v>41000</v>
-      </c>
-      <c r="D37">
-        <v>42000</v>
-      </c>
-      <c r="E37">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="B38">
-        <v>300</v>
-      </c>
-      <c r="C38">
-        <v>51000</v>
-      </c>
-      <c r="D38">
-        <v>52000</v>
-      </c>
-      <c r="E38">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="B39">
-        <v>350</v>
-      </c>
-      <c r="C39">
-        <v>59000</v>
-      </c>
-      <c r="D39">
-        <v>60000</v>
-      </c>
-      <c r="E39">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="B40">
-        <v>400</v>
-      </c>
-      <c r="C40">
-        <v>68000</v>
-      </c>
-      <c r="D40">
-        <v>69000</v>
-      </c>
-      <c r="E40">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="B41">
-        <v>450</v>
-      </c>
-      <c r="C41">
-        <v>76000</v>
-      </c>
-      <c r="D41">
-        <v>77000</v>
-      </c>
-      <c r="E41">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="B42">
-        <v>600</v>
-      </c>
-      <c r="C42">
-        <v>102000</v>
-      </c>
-      <c r="D42">
-        <v>103000</v>
-      </c>
-      <c r="E42">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="B43">
-        <v>1000</v>
-      </c>
-      <c r="C43">
-        <v>137000</v>
-      </c>
-      <c r="D43">
-        <v>138000</v>
-      </c>
-      <c r="E43">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47">
-        <v>5</v>
-      </c>
-      <c r="C47">
-        <v>340</v>
-      </c>
-      <c r="D47">
-        <v>550</v>
-      </c>
-      <c r="E47">
-        <v>12.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="B48">
-        <v>10</v>
-      </c>
-      <c r="C48">
-        <v>780</v>
-      </c>
-      <c r="D48">
-        <v>870</v>
-      </c>
-      <c r="E48">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="B49">
-        <v>15</v>
-      </c>
-      <c r="C49">
-        <v>1000</v>
-      </c>
-      <c r="D49">
-        <v>1400</v>
-      </c>
-      <c r="E49">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="B50">
-        <v>20</v>
-      </c>
-      <c r="C50">
-        <v>1500</v>
-      </c>
-      <c r="D50">
-        <v>1700</v>
-      </c>
-      <c r="E50">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51">
-        <v>25</v>
-      </c>
-      <c r="C51">
-        <v>1800</v>
-      </c>
-      <c r="D51">
-        <v>2300</v>
-      </c>
-      <c r="E51">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="B52">
-        <v>30</v>
-      </c>
-      <c r="C52">
-        <v>2200</v>
-      </c>
-      <c r="D52">
-        <v>2600</v>
-      </c>
-      <c r="E52">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="53" s="2" customFormat="1" spans="1:6">
-      <c r="B53" s="2">
-        <v>35</v>
-      </c>
-      <c r="C53" s="2">
-        <v>2500</v>
-      </c>
-      <c r="D53" s="2">
-        <v>3100</v>
-      </c>
-      <c r="E53" s="2">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>2</v>
-      </c>
-      <c r="D56" t="s">
-        <v>3</v>
-      </c>
-      <c r="E56" t="s">
-        <v>4</v>
-      </c>
-      <c r="F56" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" t="s">
-        <v>12</v>
-      </c>
-      <c r="B57">
-        <v>30</v>
-      </c>
-      <c r="C57">
-        <v>1300</v>
-      </c>
-      <c r="D57">
-        <v>1400</v>
-      </c>
-      <c r="E57">
-        <v>22.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="B58">
-        <v>35</v>
-      </c>
-      <c r="C58">
-        <v>1600</v>
-      </c>
-      <c r="D58">
-        <v>1800</v>
-      </c>
-      <c r="E58">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="B59">
-        <v>40</v>
-      </c>
-      <c r="C59">
-        <v>1800</v>
-      </c>
-      <c r="D59">
-        <v>1900</v>
-      </c>
-      <c r="E59">
-        <v>22.6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="B60">
-        <v>45</v>
-      </c>
-      <c r="C60">
-        <v>2000</v>
-      </c>
-      <c r="D60">
-        <v>2100</v>
-      </c>
-      <c r="E60">
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="B61">
-        <v>50</v>
-      </c>
-      <c r="C61">
-        <v>2200</v>
-      </c>
-      <c r="D61">
-        <v>2400</v>
-      </c>
-      <c r="E61">
-        <v>22.6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="B62">
-        <v>55</v>
-      </c>
-      <c r="C62">
-        <v>2400</v>
-      </c>
-      <c r="D62">
-        <v>2600</v>
-      </c>
-      <c r="E62">
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="B63">
-        <v>60</v>
-      </c>
-      <c r="C63">
-        <v>2600</v>
-      </c>
-      <c r="D63">
-        <v>2800</v>
-      </c>
-      <c r="E63">
-        <v>22.8</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="1:6">
-      <c r="B64" s="1">
-        <v>65</v>
-      </c>
-      <c r="C64" s="1">
-        <v>2900</v>
-      </c>
-      <c r="D64" s="1">
-        <v>3100</v>
-      </c>
-      <c r="E64" s="1">
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" t="s">
-        <v>2</v>
-      </c>
-      <c r="D67" t="s">
-        <v>3</v>
-      </c>
-      <c r="E67" t="s">
-        <v>4</v>
-      </c>
-      <c r="F67" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
-        <v>12</v>
-      </c>
-      <c r="B68">
-        <v>40</v>
-      </c>
-      <c r="C68">
-        <v>1200</v>
-      </c>
-      <c r="D68">
-        <v>1400</v>
-      </c>
-      <c r="E68">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69">
-        <v>45</v>
-      </c>
-      <c r="C69">
-        <v>1400</v>
-      </c>
-      <c r="D69">
-        <v>1600</v>
-      </c>
-      <c r="E69">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70">
-        <v>50</v>
-      </c>
-      <c r="C70">
-        <v>1500</v>
-      </c>
-      <c r="D70">
-        <v>1700</v>
-      </c>
-      <c r="E70">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71">
-        <v>55</v>
-      </c>
-      <c r="C71">
-        <v>1700</v>
-      </c>
-      <c r="D71">
-        <v>1900</v>
-      </c>
-      <c r="E71">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72">
-        <v>60</v>
-      </c>
-      <c r="C72">
-        <v>1800</v>
-      </c>
-      <c r="D72">
-        <v>2000</v>
-      </c>
-      <c r="E72">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="B73">
-        <v>65</v>
-      </c>
-      <c r="C73">
-        <v>2000</v>
-      </c>
-      <c r="D73">
-        <v>2100</v>
-      </c>
-      <c r="E73">
-        <v>32.6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74">
-        <v>70</v>
-      </c>
-      <c r="C74">
-        <v>2100</v>
-      </c>
-      <c r="D74">
-        <v>2300</v>
-      </c>
-      <c r="E74">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75">
-        <v>75</v>
-      </c>
-      <c r="C75">
-        <v>2300</v>
-      </c>
-      <c r="D75">
-        <v>2500</v>
-      </c>
-      <c r="E75">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76">
-        <v>80</v>
-      </c>
-      <c r="C76">
-        <v>2400</v>
-      </c>
-      <c r="D76">
-        <v>2600</v>
-      </c>
-      <c r="E76">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77">
-        <v>85</v>
-      </c>
-      <c r="C77">
-        <v>2600</v>
-      </c>
-      <c r="D77">
-        <v>2800</v>
-      </c>
-      <c r="E77">
-        <v>32.6</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="B78">
-        <v>90</v>
-      </c>
-      <c r="C78">
-        <v>2700</v>
-      </c>
-      <c r="D78">
-        <v>2900</v>
-      </c>
-      <c r="E78">
-        <v>32.9</v>
-      </c>
-    </row>
-    <row r="79" s="1" customFormat="1" spans="1:6">
-      <c r="B79" s="1">
-        <v>95</v>
-      </c>
-      <c r="C79" s="1">
-        <v>2900</v>
-      </c>
-      <c r="D79" s="1">
-        <v>3100</v>
-      </c>
-      <c r="E79" s="1">
-        <v>32.8</v>
-      </c>
-    </row>
+    <row r="19" s="7" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4189,78 +7102,670 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.0384615384615" customWidth="1"/>
+    <col min="2" max="2" width="10.3269230769231" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="6">
         <v>1</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="6">
         <v>2</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="6">
         <v>4</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="6">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="6">
         <v>17</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="6">
         <v>35</v>
       </c>
-      <c r="D2">
-        <v>65</v>
-      </c>
-      <c r="E2">
-        <v>95</v>
+      <c r="D2" s="6">
+        <v>70</v>
+      </c>
+      <c r="E2" s="6">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="C3" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="D3" s="6">
+        <v>26</v>
+      </c>
+      <c r="E3" s="6">
+        <v>41.6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>2</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="6">
         <v>4</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
+      <c r="B7" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="C7" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="D7" s="6">
+        <v>26</v>
+      </c>
+      <c r="E7" s="6">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="6">
+        <v>1</v>
+      </c>
+      <c r="B10" s="6">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6">
         <v>5.8</v>
       </c>
-      <c r="C7">
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="6">
+        <v>2</v>
+      </c>
+      <c r="B11" s="6">
+        <v>35</v>
+      </c>
+      <c r="C11" s="6">
         <v>12.8</v>
       </c>
-      <c r="D7">
-        <v>22.7</v>
-      </c>
-      <c r="E7">
-        <v>32.8</v>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="6">
+        <v>4</v>
+      </c>
+      <c r="B12" s="6">
+        <v>70</v>
+      </c>
+      <c r="C12" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6">
+        <v>115</v>
+      </c>
+      <c r="C13" s="6">
+        <v>41.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetData>
+    <row r="1" ht="17" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <v>300</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4">
+        <v>620</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="G3" s="3">
+        <v>3</v>
+      </c>
+      <c r="H3" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="4">
+        <v>550</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="G4" s="3">
+        <v>5</v>
+      </c>
+      <c r="H4" s="4">
+        <v>5.7</v>
+      </c>
+      <c r="I4" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1300</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="G5" s="3">
+        <v>7</v>
+      </c>
+      <c r="H5" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3">
+        <v>9</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1600</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="G6" s="3">
+        <v>9</v>
+      </c>
+      <c r="H6" s="4">
+        <v>6</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3">
+        <v>10</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1800</v>
+      </c>
+      <c r="C7" s="4">
+        <v>870</v>
+      </c>
+      <c r="D7" s="4">
+        <v>540</v>
+      </c>
+      <c r="E7" s="4">
+        <v>370</v>
+      </c>
+      <c r="G7" s="3">
+        <v>10</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5.9</v>
+      </c>
+      <c r="I7" s="4">
+        <v>13</v>
+      </c>
+      <c r="J7" s="4">
+        <v>26</v>
+      </c>
+      <c r="K7" s="4">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="3">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1900</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="G8" s="3">
+        <v>11</v>
+      </c>
+      <c r="H8" s="4">
+        <v>6</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="3">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2300</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="G9" s="3">
+        <v>13</v>
+      </c>
+      <c r="H9" s="4">
+        <v>6</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="3">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2600</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="G10" s="3">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4">
+        <v>6</v>
+      </c>
+      <c r="I10" s="4">
+        <v>13</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="3">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4">
+        <v>3000</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="G11" s="3">
+        <v>17</v>
+      </c>
+      <c r="H11" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="3">
+        <v>20</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4">
+        <v>1700</v>
+      </c>
+      <c r="D12" s="4">
+        <v>840</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="G12" s="3">
+        <v>20</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4">
+        <v>13</v>
+      </c>
+      <c r="J12" s="4">
+        <v>26</v>
+      </c>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="3">
+        <v>25</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4">
+        <v>2300</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4">
+        <v>750</v>
+      </c>
+      <c r="G13" s="3">
+        <v>25</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="3">
+        <v>30</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4">
+        <v>2600</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1300</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="G14" s="3">
+        <v>30</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="J14" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="3">
+        <v>35</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4">
+        <v>3000</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="G15" s="3">
+        <v>35</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="3">
+        <v>40</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4">
+        <v>1700</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1200</v>
+      </c>
+      <c r="G16" s="3">
+        <v>40</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4">
+        <v>26.3</v>
+      </c>
+      <c r="K16" s="4">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="3">
+        <v>50</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="G17" s="3">
+        <v>50</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
+        <v>26</v>
+      </c>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="3">
+        <v>55</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4">
+        <v>1500</v>
+      </c>
+      <c r="G18" s="3">
+        <v>55</v>
+      </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="3">
+        <v>60</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4">
+        <v>2500</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="G19" s="3">
+        <v>60</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4">
+        <v>26.7</v>
+      </c>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="3">
+        <v>70</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>70</v>
+      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4">
+        <v>26</v>
+      </c>
+      <c r="K20" s="4">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="3">
+        <v>85</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4">
+        <v>2200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>85</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="3">
+        <v>100</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4">
+        <v>2600</v>
+      </c>
+      <c r="G22" s="3">
+        <v>100</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="3">
+        <v>115</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4">
+        <v>3000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>115</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4">
+        <v>41.6</v>
       </c>
     </row>
   </sheetData>
